--- a/Parametros/Parametrizacion EOP.xlsx
+++ b/Parametros/Parametrizacion EOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://claromovilco-my.sharepoint.com/personal/38101567_claro_com_co/Documents/APOYO GERENCIA TECNICA/CCOT/JEFE CCOT/Excelencia operativa/plantilla base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{4218F7BE-8C32-45E6-8C0A-36629C4272B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{566936EC-21C7-41BC-B977-405F2D0EF6A3}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="8_{4218F7BE-8C32-45E6-8C0A-36629C4272B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23881A2F-F309-4741-B88D-D2027F4D9514}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{363D5B62-BBA4-4BCD-B4F4-D7DBBCD28D62}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{363D5B62-BBA4-4BCD-B4F4-D7DBBCD28D62}"/>
   </bookViews>
   <sheets>
     <sheet name="Regionales" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2401" uniqueCount="835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2451" uniqueCount="851">
   <si>
     <t>ID</t>
   </si>
@@ -2551,6 +2551,54 @@
   </si>
   <si>
     <t>Backoffice CCOA</t>
+  </si>
+  <si>
+    <t>Honda</t>
+  </si>
+  <si>
+    <t>pob movil</t>
+  </si>
+  <si>
+    <t>Orito</t>
+  </si>
+  <si>
+    <t>pov movil</t>
+  </si>
+  <si>
+    <t>Patia</t>
+  </si>
+  <si>
+    <t>Puerto Asis</t>
+  </si>
+  <si>
+    <t>Sibundoy</t>
+  </si>
+  <si>
+    <t>HON</t>
+  </si>
+  <si>
+    <t>HONDA</t>
+  </si>
+  <si>
+    <t>ORIT</t>
+  </si>
+  <si>
+    <t>ORITO</t>
+  </si>
+  <si>
+    <t>PATIA</t>
+  </si>
+  <si>
+    <t>PTOAS</t>
+  </si>
+  <si>
+    <t>PUERTO ASIS</t>
+  </si>
+  <si>
+    <t>SIBUN</t>
+  </si>
+  <si>
+    <t>SIBUNDOY</t>
   </si>
 </sst>
 </file>
@@ -3006,7 +3054,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0467FC96-0556-4349-859B-3BABED4DA6BC}">
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
@@ -4027,16 +4075,16 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>835</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>836</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>565</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -4045,21 +4093,21 @@
         <v>24</v>
       </c>
       <c r="G45" s="1">
-        <v>46035.627083333333</v>
+        <v>46085.805555555555</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="D46" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
@@ -4068,61 +4116,61 @@
         <v>24</v>
       </c>
       <c r="G46" s="1">
-        <v>45995.728472222225</v>
+        <v>46035.627083333333</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>654</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D47" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E47" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
       <c r="F47" t="s">
         <v>24</v>
       </c>
       <c r="G47" s="1">
-        <v>46035.616666666669</v>
+        <v>45995.728472222225</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>654</v>
       </c>
       <c r="C48" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D48" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E48" t="s">
-        <v>5</v>
+        <v>630</v>
       </c>
       <c r="F48" t="s">
         <v>24</v>
       </c>
       <c r="G48" s="1">
-        <v>46035.623611111114</v>
+        <v>46035.616666666669</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C49" t="s">
         <v>22</v>
@@ -4142,39 +4190,39 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B50" t="s">
-        <v>655</v>
+        <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>656</v>
+        <v>22</v>
       </c>
       <c r="D50" t="s">
         <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>630</v>
+        <v>5</v>
       </c>
       <c r="F50" t="s">
         <v>24</v>
       </c>
       <c r="G50" s="1">
-        <v>46059.886111111111</v>
+        <v>46035.623611111114</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C51" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D51" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="E51" t="s">
         <v>630</v>
@@ -4183,159 +4231,159 @@
         <v>24</v>
       </c>
       <c r="G51" s="1">
-        <v>46035.617361111108</v>
+        <v>46059.886111111111</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>657</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>658</v>
       </c>
       <c r="D52" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="E52" t="s">
-        <v>14</v>
+        <v>630</v>
       </c>
       <c r="F52" t="s">
         <v>24</v>
       </c>
       <c r="G52" s="1">
-        <v>46035.622916666667</v>
+        <v>46035.617361111108</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="B53" t="s">
-        <v>383</v>
+        <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>383</v>
+        <v>22</v>
       </c>
       <c r="D53" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E53" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F53" t="s">
         <v>24</v>
       </c>
       <c r="G53" s="1">
-        <v>46063.849305555559</v>
+        <v>46035.622916666667</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>383</v>
       </c>
       <c r="C54" t="s">
-        <v>62</v>
+        <v>383</v>
       </c>
       <c r="D54" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F54" t="s">
         <v>24</v>
       </c>
       <c r="G54" s="1">
-        <v>45995.728472222225</v>
+        <v>46063.849305555559</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" t="s">
         <v>27</v>
       </c>
-      <c r="B55" t="s">
-        <v>63</v>
-      </c>
-      <c r="C55" t="s">
-        <v>22</v>
-      </c>
-      <c r="D55" t="s">
-        <v>29</v>
-      </c>
       <c r="E55" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
         <v>24</v>
       </c>
       <c r="G55" s="1">
-        <v>46035.62222222222</v>
+        <v>45995.728472222225</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C56" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D56" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E56" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F56" t="s">
         <v>24</v>
       </c>
       <c r="G56" s="1">
-        <v>46035.627083333333</v>
+        <v>46035.62222222222</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B57" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C57" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D57" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E57" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F57" t="s">
         <v>24</v>
       </c>
       <c r="G57" s="1">
-        <v>46035.620833333334</v>
+        <v>46035.627083333333</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C58" t="s">
         <v>22</v>
       </c>
       <c r="D58" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E58" t="s">
         <v>12</v>
@@ -4344,21 +4392,21 @@
         <v>24</v>
       </c>
       <c r="G58" s="1">
-        <v>46035.620138888888</v>
+        <v>46035.620833333334</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C59" t="s">
         <v>22</v>
       </c>
       <c r="D59" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="E59" t="s">
         <v>12</v>
@@ -4372,16 +4420,16 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C60" t="s">
         <v>22</v>
       </c>
       <c r="D60" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E60" t="s">
         <v>12</v>
@@ -4390,44 +4438,44 @@
         <v>24</v>
       </c>
       <c r="G60" s="1">
-        <v>46035.620833333334</v>
+        <v>46035.620138888888</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C61" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="D61" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E61" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F61" t="s">
         <v>24</v>
       </c>
       <c r="G61" s="1">
-        <v>45995.727777777778</v>
+        <v>46035.620833333334</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>837</v>
       </c>
       <c r="C62" t="s">
-        <v>73</v>
+        <v>838</v>
       </c>
       <c r="D62" t="s">
-        <v>27</v>
+        <v>565</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -4436,41 +4484,41 @@
         <v>24</v>
       </c>
       <c r="G62" s="1">
-        <v>45995.729861111111</v>
+        <v>46085.806250000001</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>414</v>
+        <v>70</v>
       </c>
       <c r="C63" t="s">
-        <v>659</v>
+        <v>71</v>
       </c>
       <c r="D63" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="E63" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
       <c r="F63" t="s">
         <v>24</v>
       </c>
       <c r="G63" s="1">
-        <v>46059.90347222222</v>
+        <v>45995.727777777778</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D64" t="s">
         <v>27</v>
@@ -4482,44 +4530,44 @@
         <v>24</v>
       </c>
       <c r="G64" s="1">
-        <v>45995.729166666664</v>
+        <v>45995.729861111111</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>414</v>
       </c>
       <c r="C65" t="s">
-        <v>77</v>
+        <v>659</v>
       </c>
       <c r="D65" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="E65" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
       <c r="F65" t="s">
         <v>24</v>
       </c>
       <c r="G65" s="1">
-        <v>45995.729861111111</v>
+        <v>46059.90347222222</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="D66" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
@@ -4528,21 +4576,21 @@
         <v>24</v>
       </c>
       <c r="G66" s="1">
-        <v>46035.626388888886</v>
+        <v>45995.729166666664</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="D67" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
@@ -4551,466 +4599,581 @@
         <v>24</v>
       </c>
       <c r="G67" s="1">
-        <v>46035.628472222219</v>
+        <v>45995.729861111111</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="B68" t="s">
-        <v>442</v>
+        <v>839</v>
       </c>
       <c r="C68" t="s">
-        <v>442</v>
+        <v>836</v>
       </c>
       <c r="D68" t="s">
-        <v>23</v>
+        <v>565</v>
       </c>
       <c r="E68" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F68" t="s">
         <v>24</v>
       </c>
       <c r="G68" s="1">
-        <v>46063.848611111112</v>
+        <v>46085.806944444441</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>840</v>
       </c>
       <c r="C69" t="s">
-        <v>660</v>
+        <v>838</v>
       </c>
       <c r="D69" t="s">
-        <v>39</v>
+        <v>565</v>
       </c>
       <c r="E69" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F69" t="s">
         <v>24</v>
       </c>
       <c r="G69" s="1">
-        <v>46035.625694444447</v>
+        <v>46085.806250000001</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B70" t="s">
-        <v>458</v>
+        <v>78</v>
       </c>
       <c r="C70" t="s">
-        <v>458</v>
+        <v>22</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="E70" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F70" t="s">
         <v>24</v>
       </c>
       <c r="G70" s="1">
-        <v>46063.856944444444</v>
+        <v>46035.626388888886</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B71" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C71" t="s">
         <v>22</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E71" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F71" t="s">
         <v>24</v>
       </c>
       <c r="G71" s="1">
-        <v>46035.621527777781</v>
+        <v>46035.628472222219</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="B72" t="s">
-        <v>661</v>
+        <v>442</v>
       </c>
       <c r="C72" t="s">
-        <v>22</v>
+        <v>442</v>
       </c>
       <c r="D72" t="s">
-        <v>562</v>
+        <v>23</v>
       </c>
       <c r="E72" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F72" t="s">
         <v>24</v>
       </c>
       <c r="G72" s="1">
-        <v>46064.803472222222</v>
+        <v>46063.848611111112</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="B73" t="s">
-        <v>662</v>
+        <v>81</v>
       </c>
       <c r="C73" t="s">
-        <v>22</v>
+        <v>660</v>
       </c>
       <c r="D73" t="s">
-        <v>562</v>
+        <v>39</v>
       </c>
       <c r="E73" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F73" t="s">
         <v>24</v>
       </c>
       <c r="G73" s="1">
-        <v>46064.804166666669</v>
+        <v>46035.625694444447</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B74" t="s">
-        <v>663</v>
+        <v>458</v>
       </c>
       <c r="C74" t="s">
-        <v>22</v>
+        <v>458</v>
       </c>
       <c r="D74" t="s">
-        <v>562</v>
+        <v>23</v>
       </c>
       <c r="E74" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F74" t="s">
         <v>24</v>
       </c>
       <c r="G74" s="1">
-        <v>46064.804166666669</v>
+        <v>46063.856944444444</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="C75" t="s">
-        <v>476</v>
+        <v>22</v>
       </c>
       <c r="D75" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E75" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F75" t="s">
         <v>24</v>
       </c>
       <c r="G75" s="1">
-        <v>46063.852083333331</v>
+        <v>46035.621527777781</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>661</v>
       </c>
       <c r="C76" t="s">
         <v>22</v>
       </c>
       <c r="D76" t="s">
-        <v>39</v>
+        <v>562</v>
       </c>
       <c r="E76" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F76" t="s">
         <v>24</v>
       </c>
       <c r="G76" s="1">
-        <v>46035.625</v>
+        <v>46064.803472222222</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B77" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C77" t="s">
-        <v>664</v>
+        <v>22</v>
       </c>
       <c r="D77" t="s">
-        <v>60</v>
+        <v>562</v>
       </c>
       <c r="E77" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F77" t="s">
         <v>24</v>
       </c>
       <c r="G77" s="1">
-        <v>46063.80972222222</v>
+        <v>46064.804166666669</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B78" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C78" t="s">
-        <v>665</v>
+        <v>22</v>
       </c>
       <c r="D78" t="s">
-        <v>67</v>
+        <v>562</v>
       </c>
       <c r="E78" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F78" t="s">
         <v>24</v>
       </c>
       <c r="G78" s="1">
-        <v>46063.80972222222</v>
+        <v>46064.804166666669</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>476</v>
       </c>
       <c r="C79" t="s">
-        <v>22</v>
+        <v>476</v>
       </c>
       <c r="D79" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E79" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F79" t="s">
         <v>24</v>
       </c>
       <c r="G79" s="1">
-        <v>46035.621527777781</v>
+        <v>46063.852083333331</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C80" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="D80" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F80" t="s">
         <v>24</v>
       </c>
       <c r="G80" s="1">
-        <v>45995.727777777778</v>
+        <v>46035.625</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="B81" t="s">
-        <v>501</v>
+        <v>664</v>
       </c>
       <c r="C81" t="s">
-        <v>22</v>
+        <v>664</v>
       </c>
       <c r="D81" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="E81" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F81" t="s">
         <v>24</v>
       </c>
       <c r="G81" s="1">
-        <v>46073.802083333336</v>
+        <v>46063.80972222222</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B82" t="s">
-        <v>87</v>
+        <v>665</v>
       </c>
       <c r="C82" t="s">
-        <v>22</v>
+        <v>665</v>
       </c>
       <c r="D82" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E82" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F82" t="s">
         <v>24</v>
       </c>
       <c r="G82" s="1">
-        <v>46035.627083333333</v>
+        <v>46063.80972222222</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="B83" t="s">
-        <v>509</v>
+        <v>841</v>
       </c>
       <c r="C83" t="s">
-        <v>509</v>
+        <v>836</v>
       </c>
       <c r="D83" t="s">
-        <v>23</v>
+        <v>565</v>
       </c>
       <c r="E83" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F83" t="s">
         <v>24</v>
       </c>
       <c r="G83" s="1">
-        <v>46063.849305555559</v>
+        <v>46085.806250000001</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B84" t="s">
-        <v>515</v>
+        <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>666</v>
+        <v>22</v>
       </c>
       <c r="D84" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>630</v>
+        <v>12</v>
       </c>
       <c r="F84" t="s">
         <v>24</v>
       </c>
       <c r="G84" s="1">
-        <v>46035.618055555555</v>
+        <v>46035.621527777781</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B85" t="s">
-        <v>519</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="D85" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E85" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F85" t="s">
         <v>24</v>
       </c>
       <c r="G85" s="1">
-        <v>46035.618055555555</v>
+        <v>45995.727777777778</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>88</v>
+        <v>501</v>
       </c>
       <c r="C86" t="s">
         <v>22</v>
       </c>
       <c r="D86" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E86" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F86" t="s">
         <v>24</v>
       </c>
       <c r="G86" s="1">
-        <v>46035.62777777778</v>
+        <v>46073.802083333336</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="B87" t="s">
-        <v>526</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
         <v>22</v>
       </c>
       <c r="D87" t="s">
+        <v>54</v>
+      </c>
+      <c r="E87" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87" t="s">
+        <v>24</v>
+      </c>
+      <c r="G87" s="1">
+        <v>46035.627083333333</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>61</v>
+      </c>
+      <c r="B88" t="s">
+        <v>509</v>
+      </c>
+      <c r="C88" t="s">
+        <v>509</v>
+      </c>
+      <c r="D88" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88" t="s">
+        <v>5</v>
+      </c>
+      <c r="F88" t="s">
+        <v>24</v>
+      </c>
+      <c r="G88" s="1">
+        <v>46063.849305555559</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>16</v>
+      </c>
+      <c r="B89" t="s">
+        <v>515</v>
+      </c>
+      <c r="C89" t="s">
+        <v>666</v>
+      </c>
+      <c r="D89" t="s">
+        <v>60</v>
+      </c>
+      <c r="E89" t="s">
+        <v>630</v>
+      </c>
+      <c r="F89" t="s">
+        <v>24</v>
+      </c>
+      <c r="G89" s="1">
+        <v>46035.618055555555</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>519</v>
+      </c>
+      <c r="C90" t="s">
+        <v>38</v>
+      </c>
+      <c r="D90" t="s">
         <v>29</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E90" t="s">
         <v>14</v>
       </c>
-      <c r="F87" t="s">
-        <v>24</v>
-      </c>
-      <c r="G87" s="1">
+      <c r="F90" t="s">
+        <v>24</v>
+      </c>
+      <c r="G90" s="1">
+        <v>46035.618055555555</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>45</v>
+      </c>
+      <c r="B91" t="s">
+        <v>88</v>
+      </c>
+      <c r="C91" t="s">
+        <v>22</v>
+      </c>
+      <c r="D91" t="s">
+        <v>44</v>
+      </c>
+      <c r="E91" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" t="s">
+        <v>24</v>
+      </c>
+      <c r="G91" s="1">
+        <v>46035.62777777778</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>83</v>
+      </c>
+      <c r="B92" t="s">
+        <v>526</v>
+      </c>
+      <c r="C92" t="s">
+        <v>22</v>
+      </c>
+      <c r="D92" t="s">
+        <v>29</v>
+      </c>
+      <c r="E92" t="s">
+        <v>14</v>
+      </c>
+      <c r="F92" t="s">
+        <v>24</v>
+      </c>
+      <c r="G92" s="1">
         <v>46071.68472222222</v>
       </c>
     </row>
@@ -5024,7 +5187,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{516925B1-FB63-4D4A-831F-F6E305DE415F}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5053,7 +5215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>14</v>
       </c>
@@ -5073,7 +5235,7 @@
         <v>46029.59097222222</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5</v>
       </c>
@@ -5093,7 +5255,7 @@
         <v>45995.730555555558</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>15</v>
       </c>
@@ -5113,7 +5275,7 @@
         <v>46029.591666666667</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5133,7 +5295,7 @@
         <v>45995.730555555558</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>21</v>
       </c>
@@ -5153,7 +5315,7 @@
         <v>46029.593055555553</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>16</v>
       </c>
@@ -5173,7 +5335,7 @@
         <v>46029.591666666667</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>13</v>
       </c>
@@ -5193,7 +5355,7 @@
         <v>46029.579861111109</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>10</v>
       </c>
@@ -5213,7 +5375,7 @@
         <v>45995.731944444444</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>18</v>
       </c>
@@ -5233,7 +5395,7 @@
         <v>46029.592361111114</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>12</v>
       </c>
@@ -5253,7 +5415,7 @@
         <v>46008.813888888886</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>55</v>
       </c>
@@ -5273,7 +5435,7 @@
         <v>46067.928472222222</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>57</v>
       </c>
@@ -5293,7 +5455,7 @@
         <v>46071.688888888886</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>53</v>
       </c>
@@ -5313,7 +5475,7 @@
         <v>46067.927777777775</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>19</v>
       </c>
@@ -5333,7 +5495,7 @@
         <v>46029.592361111114</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>20</v>
       </c>
@@ -5353,7 +5515,7 @@
         <v>46029.592361111114</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>22</v>
       </c>
@@ -5373,7 +5535,7 @@
         <v>46029.593055555553</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>23</v>
       </c>
@@ -5393,7 +5555,7 @@
         <v>46029.593055555553</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -5413,7 +5575,7 @@
         <v>46029.592361111114</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>48</v>
       </c>
@@ -5433,7 +5595,7 @@
         <v>46063.870138888888</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -5453,7 +5615,7 @@
         <v>45995.730555555558</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>24</v>
       </c>
@@ -5473,7 +5635,7 @@
         <v>46029.593055555553</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>11</v>
       </c>
@@ -5493,7 +5655,7 @@
         <v>45995.731944444444</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1</v>
       </c>
@@ -5513,7 +5675,7 @@
         <v>45995.730555555558</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>54</v>
       </c>
@@ -5533,7 +5695,7 @@
         <v>46067.928472222222</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>49</v>
       </c>
@@ -5553,7 +5715,7 @@
         <v>46064.59097222222</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>34</v>
       </c>
@@ -5573,7 +5735,7 @@
         <v>46029.629861111112</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>52</v>
       </c>
@@ -5593,7 +5755,7 @@
         <v>46064.813888888886</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>51</v>
       </c>
@@ -5613,7 +5775,7 @@
         <v>46064.813888888886</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>45</v>
       </c>
@@ -5633,7 +5795,7 @@
         <v>46058.863888888889</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>25</v>
       </c>
@@ -5653,7 +5815,7 @@
         <v>46029.59375</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26</v>
       </c>
@@ -5673,7 +5835,7 @@
         <v>46029.59375</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>59</v>
       </c>
@@ -5693,7 +5855,7 @@
         <v>46071.696527777778</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>60</v>
       </c>
@@ -5753,7 +5915,7 @@
         <v>46059.844444444447</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>50</v>
       </c>
@@ -5773,7 +5935,7 @@
         <v>46064.813194444447</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -5793,7 +5955,7 @@
         <v>45995.730555555558</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>43</v>
       </c>
@@ -5813,7 +5975,7 @@
         <v>46048.916666666664</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>56</v>
       </c>
@@ -5833,7 +5995,7 @@
         <v>46069.824999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>61</v>
       </c>
@@ -5853,7 +6015,7 @@
         <v>46071.7</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>27</v>
       </c>
@@ -5873,7 +6035,7 @@
         <v>46029.595833333333</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>29</v>
       </c>
@@ -5893,7 +6055,7 @@
         <v>46029.595833333333</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>30</v>
       </c>
@@ -5913,7 +6075,7 @@
         <v>46029.59652777778</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>31</v>
       </c>
@@ -5933,7 +6095,7 @@
         <v>46029.59652777778</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>7</v>
       </c>
@@ -5953,7 +6115,7 @@
         <v>45995.731249999997</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>8</v>
       </c>
@@ -5973,7 +6135,7 @@
         <v>45995.731249999997</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>58</v>
       </c>
@@ -5993,7 +6155,7 @@
         <v>46071.693055555559</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>37</v>
       </c>
@@ -6013,7 +6175,7 @@
         <v>46045.144444444442</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>42</v>
       </c>
@@ -6033,7 +6195,7 @@
         <v>46046.191666666666</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>39</v>
       </c>
@@ -6053,7 +6215,7 @@
         <v>46045.145138888889</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>41</v>
       </c>
@@ -6073,7 +6235,7 @@
         <v>46045.145833333336</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>40</v>
       </c>
@@ -6093,7 +6255,7 @@
         <v>46045.145833333336</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>38</v>
       </c>
@@ -6113,7 +6275,7 @@
         <v>46045.145138888889</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>36</v>
       </c>
@@ -6133,7 +6295,7 @@
         <v>46045.144444444442</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>35</v>
       </c>
@@ -6153,7 +6315,7 @@
         <v>46045.144444444442</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>44</v>
       </c>
@@ -6173,7 +6335,7 @@
         <v>46057.857638888891</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>28</v>
       </c>
@@ -6193,7 +6355,7 @@
         <v>46029.595833333333</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>6</v>
       </c>
@@ -6213,7 +6375,7 @@
         <v>45995.731249999997</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>9</v>
       </c>
@@ -6233,7 +6395,7 @@
         <v>45995.731249999997</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>32</v>
       </c>
@@ -6253,7 +6415,7 @@
         <v>46029.59652777778</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>33</v>
       </c>
@@ -6274,13 +6436,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F62" xr:uid="{516925B1-FB63-4D4A-831F-F6E305DE415F}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Mantenimiento Movil"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F62" xr:uid="{516925B1-FB63-4D4A-831F-F6E305DE415F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;6&amp;K000000 Clasificación: Público. Documento Claro Colombia</oddFooter>
@@ -6491,7 +6647,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7389786F-3185-4E1A-9C61-948EBAB48956}">
-  <dimension ref="A1:E303"/>
+  <dimension ref="A1:E308"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -8893,16 +9049,16 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>329</v>
+        <v>842</v>
       </c>
       <c r="B142" t="s">
-        <v>55</v>
+        <v>843</v>
       </c>
       <c r="C142" t="s">
-        <v>93</v>
+        <v>622</v>
       </c>
       <c r="D142" t="s">
-        <v>55</v>
+        <v>835</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
@@ -8910,16 +9066,16 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B143" t="s">
         <v>55</v>
       </c>
       <c r="C143" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D143" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
@@ -8927,16 +9083,16 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B144" t="s">
-        <v>332</v>
+        <v>55</v>
       </c>
       <c r="C144" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D144" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E144" t="s">
         <v>10</v>
@@ -8944,7 +9100,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B145" t="s">
         <v>332</v>
@@ -8953,7 +9109,7 @@
         <v>93</v>
       </c>
       <c r="D145" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
@@ -8961,16 +9117,16 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>751</v>
+        <v>333</v>
       </c>
       <c r="B146" t="s">
-        <v>752</v>
+        <v>332</v>
       </c>
       <c r="C146" t="s">
         <v>93</v>
       </c>
       <c r="D146" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
@@ -8978,33 +9134,33 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>334</v>
+        <v>751</v>
       </c>
       <c r="B147" t="s">
-        <v>335</v>
+        <v>752</v>
       </c>
       <c r="C147" t="s">
         <v>93</v>
       </c>
       <c r="D147" t="s">
-        <v>654</v>
+        <v>61</v>
       </c>
       <c r="E147" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>753</v>
+        <v>334</v>
       </c>
       <c r="B148" t="s">
-        <v>754</v>
+        <v>335</v>
       </c>
       <c r="C148" t="s">
         <v>93</v>
       </c>
       <c r="D148" t="s">
-        <v>45</v>
+        <v>654</v>
       </c>
       <c r="E148" t="s">
         <v>630</v>
@@ -9012,33 +9168,33 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B149" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C149" t="s">
-        <v>716</v>
+        <v>93</v>
       </c>
       <c r="D149" t="s">
-        <v>663</v>
+        <v>45</v>
       </c>
       <c r="E149" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B150" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C150" t="s">
         <v>716</v>
       </c>
       <c r="D150" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="E150" t="s">
         <v>10</v>
@@ -9046,16 +9202,16 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>336</v>
+        <v>757</v>
       </c>
       <c r="B151" t="s">
-        <v>337</v>
+        <v>758</v>
       </c>
       <c r="C151" t="s">
-        <v>93</v>
+        <v>716</v>
       </c>
       <c r="D151" t="s">
-        <v>33</v>
+        <v>651</v>
       </c>
       <c r="E151" t="s">
         <v>10</v>
@@ -9063,16 +9219,16 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B152" t="s">
         <v>337</v>
       </c>
       <c r="C152" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D152" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="E152" t="s">
         <v>10</v>
@@ -9080,50 +9236,50 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B153" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C153" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D153" t="s">
-        <v>664</v>
+        <v>88</v>
       </c>
       <c r="E153" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B154" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C154" t="s">
         <v>93</v>
       </c>
       <c r="D154" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="E154" t="s">
-        <v>630</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B155" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C155" t="s">
         <v>93</v>
       </c>
       <c r="D155" t="s">
-        <v>515</v>
+        <v>657</v>
       </c>
       <c r="E155" t="s">
         <v>630</v>
@@ -9131,10 +9287,10 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B156" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C156" t="s">
         <v>93</v>
@@ -9148,101 +9304,101 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B157" t="s">
         <v>346</v>
       </c>
       <c r="C157" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D157" t="s">
-        <v>78</v>
+        <v>515</v>
       </c>
       <c r="E157" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>759</v>
+        <v>347</v>
       </c>
       <c r="B158" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C158" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D158" t="s">
-        <v>654</v>
+        <v>78</v>
       </c>
       <c r="E158" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>350</v>
+        <v>759</v>
       </c>
       <c r="B159" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C159" t="s">
         <v>93</v>
       </c>
       <c r="D159" t="s">
-        <v>40</v>
+        <v>654</v>
       </c>
       <c r="E159" t="s">
-        <v>14</v>
+        <v>630</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B160" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C160" t="s">
         <v>93</v>
       </c>
       <c r="D160" t="s">
-        <v>196</v>
+        <v>40</v>
       </c>
       <c r="E160" t="s">
-        <v>630</v>
+        <v>14</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B161" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C161" t="s">
         <v>93</v>
       </c>
       <c r="D161" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="E161" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B162" t="s">
         <v>355</v>
       </c>
       <c r="C162" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D162" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="E162" t="s">
         <v>10</v>
@@ -9250,16 +9406,16 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B163" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C163" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D163" t="s">
-        <v>414</v>
+        <v>64</v>
       </c>
       <c r="E163" t="s">
         <v>10</v>
@@ -9267,33 +9423,33 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>760</v>
+        <v>357</v>
       </c>
       <c r="B164" t="s">
         <v>358</v>
       </c>
       <c r="C164" t="s">
-        <v>761</v>
+        <v>93</v>
       </c>
       <c r="D164" t="s">
         <v>414</v>
       </c>
       <c r="E164" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B165" t="s">
-        <v>763</v>
+        <v>358</v>
       </c>
       <c r="C165" t="s">
         <v>761</v>
       </c>
       <c r="D165" t="s">
-        <v>654</v>
+        <v>414</v>
       </c>
       <c r="E165" t="s">
         <v>630</v>
@@ -9301,95 +9457,95 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B166" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C166" t="s">
-        <v>93</v>
+        <v>761</v>
       </c>
       <c r="D166" t="s">
-        <v>476</v>
+        <v>654</v>
       </c>
       <c r="E166" t="s">
-        <v>5</v>
+        <v>630</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>360</v>
+        <v>764</v>
       </c>
       <c r="B167" t="s">
-        <v>361</v>
+        <v>765</v>
       </c>
       <c r="C167" t="s">
         <v>93</v>
       </c>
       <c r="D167" t="s">
-        <v>657</v>
+        <v>476</v>
       </c>
       <c r="E167" t="s">
-        <v>630</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B168" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C168" t="s">
         <v>93</v>
       </c>
       <c r="D168" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="E168" t="s">
-        <v>12</v>
+        <v>630</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B169" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C169" t="s">
         <v>93</v>
       </c>
       <c r="D169" t="s">
-        <v>476</v>
+        <v>665</v>
       </c>
       <c r="E169" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B170" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C170" t="s">
         <v>93</v>
       </c>
       <c r="D170" t="s">
-        <v>515</v>
+        <v>476</v>
       </c>
       <c r="E170" t="s">
-        <v>630</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B171" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C171" t="s">
         <v>93</v>
@@ -9403,16 +9559,16 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B172" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C172" t="s">
         <v>93</v>
       </c>
       <c r="D172" t="s">
-        <v>657</v>
+        <v>515</v>
       </c>
       <c r="E172" t="s">
         <v>630</v>
@@ -9420,44 +9576,44 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>766</v>
+        <v>370</v>
       </c>
       <c r="B173" t="s">
-        <v>767</v>
+        <v>371</v>
       </c>
       <c r="C173" t="s">
         <v>93</v>
       </c>
       <c r="D173" t="s">
-        <v>55</v>
+        <v>657</v>
       </c>
       <c r="E173" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>372</v>
+        <v>766</v>
       </c>
       <c r="B174" t="s">
-        <v>373</v>
+        <v>767</v>
       </c>
       <c r="C174" t="s">
         <v>93</v>
       </c>
       <c r="D174" t="s">
-        <v>515</v>
+        <v>55</v>
       </c>
       <c r="E174" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B175" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C175" t="s">
         <v>93</v>
@@ -9471,10 +9627,10 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>768</v>
+        <v>374</v>
       </c>
       <c r="B176" t="s">
-        <v>769</v>
+        <v>375</v>
       </c>
       <c r="C176" t="s">
         <v>93</v>
@@ -9488,16 +9644,16 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B177" t="s">
-        <v>655</v>
+        <v>769</v>
       </c>
       <c r="C177" t="s">
         <v>93</v>
       </c>
       <c r="D177" t="s">
-        <v>45</v>
+        <v>515</v>
       </c>
       <c r="E177" t="s">
         <v>630</v>
@@ -9505,16 +9661,16 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>376</v>
+        <v>770</v>
       </c>
       <c r="B178" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C178" t="s">
         <v>93</v>
       </c>
       <c r="D178" t="s">
-        <v>657</v>
+        <v>45</v>
       </c>
       <c r="E178" t="s">
         <v>630</v>
@@ -9522,33 +9678,33 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B179" t="s">
-        <v>378</v>
+        <v>657</v>
       </c>
       <c r="C179" t="s">
         <v>93</v>
       </c>
       <c r="D179" t="s">
-        <v>46</v>
+        <v>657</v>
       </c>
       <c r="E179" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B180" t="s">
         <v>378</v>
       </c>
       <c r="C180" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D180" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="E180" t="s">
         <v>10</v>
@@ -9556,101 +9712,101 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B181" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C181" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D181" t="s">
-        <v>196</v>
+        <v>87</v>
       </c>
       <c r="E181" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B182" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C182" t="s">
         <v>93</v>
       </c>
       <c r="D182" t="s">
-        <v>383</v>
+        <v>196</v>
       </c>
       <c r="E182" t="s">
-        <v>5</v>
+        <v>630</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B183" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C183" t="s">
         <v>93</v>
       </c>
       <c r="D183" t="s">
-        <v>665</v>
+        <v>383</v>
       </c>
       <c r="E183" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B184" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C184" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D184" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="E184" t="s">
-        <v>630</v>
+        <v>12</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>771</v>
+        <v>386</v>
       </c>
       <c r="B185" t="s">
-        <v>772</v>
+        <v>387</v>
       </c>
       <c r="C185" t="s">
-        <v>716</v>
+        <v>134</v>
       </c>
       <c r="D185" t="s">
-        <v>635</v>
+        <v>657</v>
       </c>
       <c r="E185" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B186" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C186" t="s">
         <v>716</v>
       </c>
       <c r="D186" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E186" t="s">
         <v>10</v>
@@ -9658,67 +9814,67 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B187" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C187" t="s">
-        <v>93</v>
+        <v>716</v>
       </c>
       <c r="D187" t="s">
-        <v>476</v>
+        <v>634</v>
       </c>
       <c r="E187" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>388</v>
+        <v>775</v>
       </c>
       <c r="B188" t="s">
-        <v>389</v>
+        <v>776</v>
       </c>
       <c r="C188" t="s">
         <v>93</v>
       </c>
       <c r="D188" t="s">
-        <v>515</v>
+        <v>476</v>
       </c>
       <c r="E188" t="s">
-        <v>630</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B189" t="s">
-        <v>61</v>
+        <v>389</v>
       </c>
       <c r="C189" t="s">
         <v>93</v>
       </c>
       <c r="D189" t="s">
-        <v>61</v>
+        <v>515</v>
       </c>
       <c r="E189" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B190" t="s">
         <v>61</v>
       </c>
       <c r="C190" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D190" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="E190" t="s">
         <v>10</v>
@@ -9726,84 +9882,84 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B191" t="s">
-        <v>393</v>
+        <v>61</v>
       </c>
       <c r="C191" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D191" t="s">
-        <v>664</v>
+        <v>87</v>
       </c>
       <c r="E191" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B192" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C192" t="s">
         <v>93</v>
       </c>
       <c r="D192" t="s">
-        <v>515</v>
+        <v>664</v>
       </c>
       <c r="E192" t="s">
-        <v>630</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>777</v>
+        <v>394</v>
       </c>
       <c r="B193" t="s">
-        <v>778</v>
+        <v>395</v>
       </c>
       <c r="C193" t="s">
-        <v>716</v>
+        <v>93</v>
       </c>
       <c r="D193" t="s">
-        <v>635</v>
+        <v>515</v>
       </c>
       <c r="E193" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>396</v>
+        <v>777</v>
       </c>
       <c r="B194" t="s">
-        <v>397</v>
+        <v>778</v>
       </c>
       <c r="C194" t="s">
-        <v>93</v>
+        <v>716</v>
       </c>
       <c r="D194" t="s">
-        <v>82</v>
+        <v>635</v>
       </c>
       <c r="E194" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B195" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C195" t="s">
         <v>93</v>
       </c>
       <c r="D195" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="E195" t="s">
         <v>14</v>
@@ -9811,67 +9967,67 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>402</v>
+        <v>844</v>
       </c>
       <c r="B196" t="s">
-        <v>403</v>
+        <v>845</v>
       </c>
       <c r="C196" t="s">
-        <v>93</v>
+        <v>622</v>
       </c>
       <c r="D196" t="s">
-        <v>515</v>
+        <v>837</v>
       </c>
       <c r="E196" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B197" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C197" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D197" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="E197" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B198" t="s">
-        <v>70</v>
+        <v>403</v>
       </c>
       <c r="C198" t="s">
         <v>93</v>
       </c>
       <c r="D198" t="s">
-        <v>70</v>
+        <v>515</v>
       </c>
       <c r="E198" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B199" t="s">
-        <v>70</v>
+        <v>403</v>
       </c>
       <c r="C199" t="s">
         <v>134</v>
       </c>
       <c r="D199" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="E199" t="s">
         <v>10</v>
@@ -9879,33 +10035,33 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B200" t="s">
-        <v>408</v>
+        <v>70</v>
       </c>
       <c r="C200" t="s">
         <v>93</v>
       </c>
       <c r="D200" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E200" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B201" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C201" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D201" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E201" t="s">
         <v>10</v>
@@ -9913,135 +10069,135 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B202" t="s">
-        <v>72</v>
+        <v>408</v>
       </c>
       <c r="C202" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D202" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E202" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B203" t="s">
-        <v>412</v>
+        <v>72</v>
       </c>
       <c r="C203" t="s">
         <v>93</v>
       </c>
       <c r="D203" t="s">
-        <v>515</v>
+        <v>72</v>
       </c>
       <c r="E203" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B204" t="s">
-        <v>414</v>
+        <v>72</v>
       </c>
       <c r="C204" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D204" t="s">
-        <v>414</v>
+        <v>64</v>
       </c>
       <c r="E204" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>415</v>
+        <v>846</v>
       </c>
       <c r="B205" t="s">
-        <v>416</v>
+        <v>846</v>
       </c>
       <c r="C205" t="s">
-        <v>93</v>
+        <v>622</v>
       </c>
       <c r="D205" t="s">
-        <v>28</v>
+        <v>839</v>
       </c>
       <c r="E205" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B206" t="s">
-        <v>74</v>
+        <v>412</v>
       </c>
       <c r="C206" t="s">
         <v>93</v>
       </c>
       <c r="D206" t="s">
-        <v>74</v>
+        <v>515</v>
       </c>
       <c r="E206" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B207" t="s">
-        <v>74</v>
+        <v>414</v>
       </c>
       <c r="C207" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D207" t="s">
-        <v>53</v>
+        <v>414</v>
       </c>
       <c r="E207" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B208" t="s">
-        <v>76</v>
+        <v>416</v>
       </c>
       <c r="C208" t="s">
         <v>93</v>
       </c>
       <c r="D208" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="E208" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B209" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C209" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D209" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="E209" t="s">
         <v>10</v>
@@ -10049,16 +10205,16 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B210" t="s">
-        <v>422</v>
+        <v>74</v>
       </c>
       <c r="C210" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D210" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="E210" t="s">
         <v>10</v>
@@ -10066,16 +10222,16 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B211" t="s">
-        <v>422</v>
+        <v>76</v>
       </c>
       <c r="C211" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D211" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E211" t="s">
         <v>10</v>
@@ -10083,84 +10239,84 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B212" t="s">
-        <v>425</v>
+        <v>76</v>
       </c>
       <c r="C212" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D212" t="s">
-        <v>515</v>
+        <v>43</v>
       </c>
       <c r="E212" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>779</v>
+        <v>421</v>
       </c>
       <c r="B213" t="s">
-        <v>780</v>
+        <v>422</v>
       </c>
       <c r="C213" t="s">
         <v>93</v>
       </c>
       <c r="D213" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="E213" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B214" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C214" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D214" t="s">
-        <v>632</v>
+        <v>88</v>
       </c>
       <c r="E214" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B215" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C215" t="s">
         <v>93</v>
       </c>
       <c r="D215" t="s">
-        <v>33</v>
+        <v>515</v>
       </c>
       <c r="E215" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>430</v>
+        <v>847</v>
       </c>
       <c r="B216" t="s">
-        <v>429</v>
+        <v>848</v>
       </c>
       <c r="C216" t="s">
-        <v>134</v>
+        <v>622</v>
       </c>
       <c r="D216" t="s">
-        <v>43</v>
+        <v>840</v>
       </c>
       <c r="E216" t="s">
         <v>10</v>
@@ -10168,10 +10324,10 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B217" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C217" t="s">
         <v>93</v>
@@ -10185,84 +10341,84 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>783</v>
+        <v>426</v>
       </c>
       <c r="B218" t="s">
-        <v>784</v>
+        <v>427</v>
       </c>
       <c r="C218" t="s">
         <v>93</v>
       </c>
       <c r="D218" t="s">
-        <v>55</v>
+        <v>632</v>
       </c>
       <c r="E218" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="B219" t="s">
-        <v>785</v>
+        <v>429</v>
       </c>
       <c r="C219" t="s">
         <v>93</v>
       </c>
       <c r="D219" t="s">
-        <v>316</v>
+        <v>33</v>
       </c>
       <c r="E219" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>399</v>
+        <v>430</v>
       </c>
       <c r="B220" t="s">
-        <v>786</v>
+        <v>429</v>
       </c>
       <c r="C220" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D220" t="s">
-        <v>280</v>
+        <v>43</v>
       </c>
       <c r="E220" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="B221" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="C221" t="s">
         <v>93</v>
       </c>
       <c r="D221" t="s">
-        <v>280</v>
+        <v>45</v>
       </c>
       <c r="E221" t="s">
-        <v>14</v>
+        <v>630</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="B222" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="C222" t="s">
-        <v>716</v>
+        <v>93</v>
       </c>
       <c r="D222" t="s">
-        <v>636</v>
+        <v>55</v>
       </c>
       <c r="E222" t="s">
         <v>10</v>
@@ -10270,67 +10426,67 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>791</v>
+        <v>398</v>
       </c>
       <c r="B223" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="C223" t="s">
-        <v>716</v>
+        <v>93</v>
       </c>
       <c r="D223" t="s">
-        <v>653</v>
+        <v>316</v>
       </c>
       <c r="E223" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>793</v>
+        <v>399</v>
       </c>
       <c r="B224" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="C224" t="s">
-        <v>716</v>
+        <v>93</v>
       </c>
       <c r="D224" t="s">
-        <v>635</v>
+        <v>280</v>
       </c>
       <c r="E224" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="B225" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="C225" t="s">
         <v>93</v>
       </c>
       <c r="D225" t="s">
-        <v>37</v>
+        <v>280</v>
       </c>
       <c r="E225" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="B226" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="C226" t="s">
         <v>716</v>
       </c>
       <c r="D226" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E226" t="s">
         <v>10</v>
@@ -10338,186 +10494,186 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="B227" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="C227" t="s">
-        <v>93</v>
+        <v>716</v>
       </c>
       <c r="D227" t="s">
-        <v>37</v>
+        <v>653</v>
       </c>
       <c r="E227" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>431</v>
+        <v>793</v>
       </c>
       <c r="B228" t="s">
-        <v>432</v>
+        <v>794</v>
       </c>
       <c r="C228" t="s">
-        <v>93</v>
+        <v>716</v>
       </c>
       <c r="D228" t="s">
-        <v>196</v>
+        <v>635</v>
       </c>
       <c r="E228" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>433</v>
+        <v>795</v>
       </c>
       <c r="B229" t="s">
-        <v>434</v>
+        <v>796</v>
       </c>
       <c r="C229" t="s">
         <v>93</v>
       </c>
       <c r="D229" t="s">
-        <v>515</v>
+        <v>37</v>
       </c>
       <c r="E229" t="s">
-        <v>630</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>435</v>
+        <v>797</v>
       </c>
       <c r="B230" t="s">
-        <v>436</v>
+        <v>798</v>
       </c>
       <c r="C230" t="s">
-        <v>93</v>
+        <v>716</v>
       </c>
       <c r="D230" t="s">
-        <v>59</v>
+        <v>637</v>
       </c>
       <c r="E230" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>437</v>
+        <v>799</v>
       </c>
       <c r="B231" t="s">
-        <v>436</v>
+        <v>800</v>
       </c>
       <c r="C231" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D231" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="E231" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="B232" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="C232" t="s">
         <v>93</v>
       </c>
       <c r="D232" t="s">
-        <v>26</v>
+        <v>196</v>
       </c>
       <c r="E232" t="s">
-        <v>14</v>
+        <v>630</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="B233" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C233" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D233" t="s">
-        <v>64</v>
+        <v>515</v>
       </c>
       <c r="E233" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B234" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C234" t="s">
         <v>93</v>
       </c>
       <c r="D234" t="s">
-        <v>442</v>
+        <v>59</v>
       </c>
       <c r="E234" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>801</v>
+        <v>437</v>
       </c>
       <c r="B235" t="s">
-        <v>802</v>
+        <v>436</v>
       </c>
       <c r="C235" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D235" t="s">
-        <v>657</v>
+        <v>88</v>
       </c>
       <c r="E235" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B236" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C236" t="s">
         <v>93</v>
       </c>
       <c r="D236" t="s">
-        <v>515</v>
+        <v>26</v>
       </c>
       <c r="E236" t="s">
-        <v>630</v>
+        <v>14</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B237" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="C237" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D237" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="E237" t="s">
         <v>10</v>
@@ -10525,33 +10681,33 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B238" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C238" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D238" t="s">
-        <v>88</v>
+        <v>442</v>
       </c>
       <c r="E238" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>448</v>
+        <v>801</v>
       </c>
       <c r="B239" t="s">
-        <v>449</v>
+        <v>802</v>
       </c>
       <c r="C239" t="s">
         <v>93</v>
       </c>
       <c r="D239" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="E239" t="s">
         <v>630</v>
@@ -10559,254 +10715,254 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="B240" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="C240" t="s">
         <v>93</v>
       </c>
       <c r="D240" t="s">
-        <v>383</v>
+        <v>515</v>
       </c>
       <c r="E240" t="s">
-        <v>5</v>
+        <v>630</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>803</v>
+        <v>445</v>
       </c>
       <c r="B241" t="s">
-        <v>804</v>
+        <v>446</v>
       </c>
       <c r="C241" t="s">
         <v>93</v>
       </c>
       <c r="D241" t="s">
-        <v>515</v>
+        <v>85</v>
       </c>
       <c r="E241" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B242" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C242" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D242" t="s">
-        <v>515</v>
+        <v>88</v>
       </c>
       <c r="E242" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>805</v>
+        <v>448</v>
       </c>
       <c r="B243" t="s">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="C243" t="s">
         <v>93</v>
       </c>
       <c r="D243" t="s">
-        <v>81</v>
+        <v>654</v>
       </c>
       <c r="E243" t="s">
-        <v>5</v>
+        <v>630</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>806</v>
+        <v>450</v>
       </c>
       <c r="B244" t="s">
-        <v>807</v>
+        <v>451</v>
       </c>
       <c r="C244" t="s">
         <v>93</v>
       </c>
       <c r="D244" t="s">
-        <v>654</v>
+        <v>383</v>
       </c>
       <c r="E244" t="s">
-        <v>630</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>455</v>
+        <v>803</v>
       </c>
       <c r="B245" t="s">
-        <v>456</v>
+        <v>804</v>
       </c>
       <c r="C245" t="s">
         <v>93</v>
       </c>
       <c r="D245" t="s">
-        <v>40</v>
+        <v>515</v>
       </c>
       <c r="E245" t="s">
-        <v>14</v>
+        <v>630</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>359</v>
+        <v>452</v>
       </c>
       <c r="B246" t="s">
-        <v>808</v>
+        <v>453</v>
       </c>
       <c r="C246" t="s">
         <v>93</v>
       </c>
       <c r="D246" t="s">
-        <v>272</v>
+        <v>515</v>
       </c>
       <c r="E246" t="s">
-        <v>14</v>
+        <v>630</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="B247" t="s">
-        <v>808</v>
+        <v>81</v>
       </c>
       <c r="C247" t="s">
         <v>93</v>
       </c>
       <c r="D247" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="E247" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>457</v>
+        <v>806</v>
       </c>
       <c r="B248" t="s">
-        <v>458</v>
+        <v>807</v>
       </c>
       <c r="C248" t="s">
         <v>93</v>
       </c>
       <c r="D248" t="s">
-        <v>458</v>
+        <v>654</v>
       </c>
       <c r="E248" t="s">
-        <v>5</v>
+        <v>630</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B249" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C249" t="s">
         <v>93</v>
       </c>
       <c r="D249" t="s">
-        <v>414</v>
+        <v>40</v>
       </c>
       <c r="E249" t="s">
-        <v>630</v>
+        <v>14</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>810</v>
+        <v>359</v>
       </c>
       <c r="B250" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C250" t="s">
         <v>93</v>
       </c>
       <c r="D250" t="s">
-        <v>45</v>
+        <v>272</v>
       </c>
       <c r="E250" t="s">
-        <v>630</v>
+        <v>14</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="B251" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C251" t="s">
         <v>93</v>
       </c>
       <c r="D251" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E251" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B252" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C252" t="s">
         <v>93</v>
       </c>
       <c r="D252" t="s">
-        <v>33</v>
+        <v>458</v>
       </c>
       <c r="E252" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B253" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C253" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D253" t="s">
-        <v>43</v>
+        <v>414</v>
       </c>
       <c r="E253" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>464</v>
+        <v>810</v>
       </c>
       <c r="B254" t="s">
-        <v>465</v>
+        <v>811</v>
       </c>
       <c r="C254" t="s">
         <v>93</v>
       </c>
       <c r="D254" t="s">
-        <v>657</v>
+        <v>45</v>
       </c>
       <c r="E254" t="s">
         <v>630</v>
@@ -10814,33 +10970,33 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>466</v>
+        <v>812</v>
       </c>
       <c r="B255" t="s">
-        <v>467</v>
+        <v>811</v>
       </c>
       <c r="C255" t="s">
         <v>93</v>
       </c>
       <c r="D255" t="s">
-        <v>664</v>
+        <v>45</v>
       </c>
       <c r="E255" t="s">
-        <v>12</v>
+        <v>630</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="B256" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="C256" t="s">
         <v>93</v>
       </c>
       <c r="D256" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="E256" t="s">
         <v>10</v>
@@ -10848,16 +11004,16 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="B257" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="C257" t="s">
         <v>134</v>
       </c>
       <c r="D257" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="E257" t="s">
         <v>10</v>
@@ -10865,152 +11021,152 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="B258" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="C258" t="s">
         <v>93</v>
       </c>
       <c r="D258" t="s">
-        <v>642</v>
+        <v>657</v>
       </c>
       <c r="E258" t="s">
-        <v>12</v>
+        <v>630</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="B259" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="C259" t="s">
         <v>93</v>
       </c>
       <c r="D259" t="s">
-        <v>26</v>
+        <v>664</v>
       </c>
       <c r="E259" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="B260" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="C260" t="s">
         <v>93</v>
       </c>
       <c r="D260" t="s">
-        <v>476</v>
+        <v>85</v>
       </c>
       <c r="E260" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B261" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="C261" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D261" t="s">
-        <v>642</v>
+        <v>88</v>
       </c>
       <c r="E261" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="B262" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="C262" t="s">
         <v>93</v>
       </c>
       <c r="D262" t="s">
-        <v>82</v>
+        <v>642</v>
       </c>
       <c r="E262" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>482</v>
+        <v>849</v>
       </c>
       <c r="B263" t="s">
-        <v>483</v>
+        <v>850</v>
       </c>
       <c r="C263" t="s">
-        <v>93</v>
+        <v>622</v>
       </c>
       <c r="D263" t="s">
-        <v>21</v>
+        <v>841</v>
       </c>
       <c r="E263" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B264" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="C264" t="s">
         <v>93</v>
       </c>
       <c r="D264" t="s">
-        <v>664</v>
+        <v>26</v>
       </c>
       <c r="E264" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>813</v>
+        <v>475</v>
       </c>
       <c r="B265" t="s">
-        <v>814</v>
+        <v>476</v>
       </c>
       <c r="C265" t="s">
         <v>93</v>
       </c>
       <c r="D265" t="s">
-        <v>61</v>
+        <v>476</v>
       </c>
       <c r="E265" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="B266" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="C266" t="s">
         <v>93</v>
       </c>
       <c r="D266" t="s">
-        <v>665</v>
+        <v>642</v>
       </c>
       <c r="E266" t="s">
         <v>12</v>
@@ -11018,84 +11174,84 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="B267" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C267" t="s">
         <v>93</v>
       </c>
       <c r="D267" t="s">
-        <v>664</v>
+        <v>82</v>
       </c>
       <c r="E267" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="B268" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="C268" t="s">
         <v>93</v>
       </c>
       <c r="D268" t="s">
-        <v>515</v>
+        <v>21</v>
       </c>
       <c r="E268" t="s">
-        <v>630</v>
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="B269" t="s">
-        <v>815</v>
+        <v>485</v>
       </c>
       <c r="C269" t="s">
         <v>93</v>
       </c>
       <c r="D269" t="s">
-        <v>643</v>
+        <v>664</v>
       </c>
       <c r="E269" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>481</v>
+        <v>813</v>
       </c>
       <c r="B270" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C270" t="s">
         <v>93</v>
       </c>
       <c r="D270" t="s">
-        <v>280</v>
+        <v>61</v>
       </c>
       <c r="E270" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B271" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="C271" t="s">
         <v>93</v>
       </c>
       <c r="D271" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E271" t="s">
         <v>12</v>
@@ -11103,152 +11259,152 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>817</v>
+        <v>488</v>
       </c>
       <c r="B272" t="s">
-        <v>818</v>
+        <v>489</v>
       </c>
       <c r="C272" t="s">
         <v>93</v>
       </c>
       <c r="D272" t="s">
-        <v>45</v>
+        <v>664</v>
       </c>
       <c r="E272" t="s">
-        <v>630</v>
+        <v>12</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B273" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C273" t="s">
         <v>93</v>
       </c>
       <c r="D273" t="s">
-        <v>664</v>
+        <v>515</v>
       </c>
       <c r="E273" t="s">
-        <v>12</v>
+        <v>630</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>496</v>
+        <v>454</v>
       </c>
       <c r="B274" t="s">
-        <v>497</v>
+        <v>815</v>
       </c>
       <c r="C274" t="s">
         <v>93</v>
       </c>
       <c r="D274" t="s">
-        <v>664</v>
+        <v>643</v>
       </c>
       <c r="E274" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="B275" t="s">
-        <v>85</v>
+        <v>816</v>
       </c>
       <c r="C275" t="s">
         <v>93</v>
       </c>
       <c r="D275" t="s">
-        <v>85</v>
+        <v>280</v>
       </c>
       <c r="E275" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B276" t="s">
-        <v>85</v>
+        <v>493</v>
       </c>
       <c r="C276" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D276" t="s">
-        <v>88</v>
+        <v>664</v>
       </c>
       <c r="E276" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>502</v>
+        <v>817</v>
       </c>
       <c r="B277" t="s">
-        <v>503</v>
+        <v>818</v>
       </c>
       <c r="C277" t="s">
         <v>93</v>
       </c>
       <c r="D277" t="s">
-        <v>236</v>
+        <v>45</v>
       </c>
       <c r="E277" t="s">
-        <v>5</v>
+        <v>630</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="B278" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C278" t="s">
         <v>93</v>
       </c>
       <c r="D278" t="s">
-        <v>190</v>
+        <v>664</v>
       </c>
       <c r="E278" t="s">
-        <v>630</v>
+        <v>12</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>819</v>
+        <v>496</v>
       </c>
       <c r="B279" t="s">
-        <v>820</v>
+        <v>497</v>
       </c>
       <c r="C279" t="s">
-        <v>716</v>
+        <v>93</v>
       </c>
       <c r="D279" t="s">
-        <v>638</v>
+        <v>664</v>
       </c>
       <c r="E279" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>821</v>
+        <v>498</v>
       </c>
       <c r="B280" t="s">
-        <v>822</v>
+        <v>85</v>
       </c>
       <c r="C280" t="s">
-        <v>716</v>
+        <v>93</v>
       </c>
       <c r="D280" t="s">
-        <v>652</v>
+        <v>85</v>
       </c>
       <c r="E280" t="s">
         <v>10</v>
@@ -11256,50 +11412,50 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B281" t="s">
-        <v>823</v>
+        <v>85</v>
       </c>
       <c r="C281" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D281" t="s">
-        <v>501</v>
+        <v>88</v>
       </c>
       <c r="E281" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B282" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C282" t="s">
         <v>93</v>
       </c>
       <c r="D282" t="s">
-        <v>657</v>
+        <v>236</v>
       </c>
       <c r="E282" t="s">
-        <v>630</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>824</v>
+        <v>504</v>
       </c>
       <c r="B283" t="s">
-        <v>825</v>
+        <v>505</v>
       </c>
       <c r="C283" t="s">
         <v>93</v>
       </c>
       <c r="D283" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="E283" t="s">
         <v>630</v>
@@ -11307,50 +11463,50 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>508</v>
+        <v>819</v>
       </c>
       <c r="B284" t="s">
-        <v>509</v>
+        <v>820</v>
       </c>
       <c r="C284" t="s">
-        <v>93</v>
+        <v>716</v>
       </c>
       <c r="D284" t="s">
-        <v>509</v>
+        <v>638</v>
       </c>
       <c r="E284" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="B285" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="C285" t="s">
-        <v>93</v>
+        <v>716</v>
       </c>
       <c r="D285" t="s">
-        <v>515</v>
+        <v>652</v>
       </c>
       <c r="E285" t="s">
-        <v>630</v>
+        <v>10</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="B286" t="s">
-        <v>513</v>
+        <v>823</v>
       </c>
       <c r="C286" t="s">
         <v>93</v>
       </c>
       <c r="D286" t="s">
-        <v>63</v>
+        <v>501</v>
       </c>
       <c r="E286" t="s">
         <v>14</v>
@@ -11358,16 +11514,16 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="B287" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="C287" t="s">
         <v>93</v>
       </c>
       <c r="D287" t="s">
-        <v>515</v>
+        <v>657</v>
       </c>
       <c r="E287" t="s">
         <v>630</v>
@@ -11375,44 +11531,44 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>516</v>
+        <v>824</v>
       </c>
       <c r="B288" t="s">
-        <v>517</v>
+        <v>825</v>
       </c>
       <c r="C288" t="s">
         <v>93</v>
       </c>
       <c r="D288" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E288" t="s">
-        <v>14</v>
+        <v>630</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="B289" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="C289" t="s">
         <v>93</v>
       </c>
       <c r="D289" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="E289" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>521</v>
+        <v>826</v>
       </c>
       <c r="B290" t="s">
-        <v>522</v>
+        <v>827</v>
       </c>
       <c r="C290" t="s">
         <v>93</v>
@@ -11426,16 +11582,16 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B291" t="s">
-        <v>828</v>
+        <v>513</v>
       </c>
       <c r="C291" t="s">
         <v>93</v>
       </c>
       <c r="D291" t="s">
-        <v>501</v>
+        <v>63</v>
       </c>
       <c r="E291" t="s">
         <v>14</v>
@@ -11443,33 +11599,33 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B292" t="s">
-        <v>829</v>
+        <v>515</v>
       </c>
       <c r="C292" t="s">
         <v>93</v>
       </c>
       <c r="D292" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="E292" t="s">
-        <v>14</v>
+        <v>630</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B293" t="s">
-        <v>830</v>
+        <v>517</v>
       </c>
       <c r="C293" t="s">
         <v>93</v>
       </c>
       <c r="D293" t="s">
-        <v>316</v>
+        <v>63</v>
       </c>
       <c r="E293" t="s">
         <v>14</v>
@@ -11477,33 +11633,33 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>287</v>
+        <v>518</v>
       </c>
       <c r="B294" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="C294" t="s">
         <v>93</v>
       </c>
       <c r="D294" t="s">
-        <v>654</v>
+        <v>519</v>
       </c>
       <c r="E294" t="s">
-        <v>630</v>
+        <v>14</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>348</v>
+        <v>521</v>
       </c>
       <c r="B295" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C295" t="s">
         <v>93</v>
       </c>
       <c r="D295" t="s">
-        <v>654</v>
+        <v>515</v>
       </c>
       <c r="E295" t="s">
         <v>630</v>
@@ -11511,33 +11667,33 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="B296" t="s">
-        <v>524</v>
+        <v>828</v>
       </c>
       <c r="C296" t="s">
         <v>93</v>
       </c>
       <c r="D296" t="s">
-        <v>657</v>
+        <v>501</v>
       </c>
       <c r="E296" t="s">
-        <v>630</v>
+        <v>14</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="B297" t="s">
-        <v>526</v>
+        <v>829</v>
       </c>
       <c r="C297" t="s">
         <v>93</v>
       </c>
       <c r="D297" t="s">
-        <v>526</v>
+        <v>501</v>
       </c>
       <c r="E297" t="s">
         <v>14</v>
@@ -11545,103 +11701,188 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="B298" t="s">
-        <v>528</v>
+        <v>830</v>
       </c>
       <c r="C298" t="s">
         <v>93</v>
       </c>
       <c r="D298" t="s">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="E298" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>529</v>
+        <v>287</v>
       </c>
       <c r="B299" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C299" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D299" t="s">
-        <v>88</v>
+        <v>654</v>
       </c>
       <c r="E299" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>831</v>
+        <v>348</v>
       </c>
       <c r="B300" t="s">
-        <v>832</v>
+        <v>524</v>
       </c>
       <c r="C300" t="s">
-        <v>716</v>
+        <v>93</v>
       </c>
       <c r="D300" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="E300" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B301" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="C301" t="s">
         <v>93</v>
       </c>
       <c r="D301" t="s">
-        <v>85</v>
+        <v>657</v>
       </c>
       <c r="E301" t="s">
-        <v>10</v>
+        <v>630</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="B302" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C302" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D302" t="s">
-        <v>88</v>
+        <v>526</v>
       </c>
       <c r="E302" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
+        <v>527</v>
+      </c>
+      <c r="B303" t="s">
+        <v>528</v>
+      </c>
+      <c r="C303" t="s">
+        <v>93</v>
+      </c>
+      <c r="D303" t="s">
+        <v>30</v>
+      </c>
+      <c r="E303" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>529</v>
+      </c>
+      <c r="B304" t="s">
+        <v>528</v>
+      </c>
+      <c r="C304" t="s">
+        <v>134</v>
+      </c>
+      <c r="D304" t="s">
+        <v>88</v>
+      </c>
+      <c r="E304" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>831</v>
+      </c>
+      <c r="B305" t="s">
+        <v>832</v>
+      </c>
+      <c r="C305" t="s">
+        <v>716</v>
+      </c>
+      <c r="D305" t="s">
+        <v>662</v>
+      </c>
+      <c r="E305" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>530</v>
+      </c>
+      <c r="B306" t="s">
+        <v>531</v>
+      </c>
+      <c r="C306" t="s">
+        <v>93</v>
+      </c>
+      <c r="D306" t="s">
+        <v>85</v>
+      </c>
+      <c r="E306" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>532</v>
+      </c>
+      <c r="B307" t="s">
+        <v>531</v>
+      </c>
+      <c r="C307" t="s">
+        <v>134</v>
+      </c>
+      <c r="D307" t="s">
+        <v>88</v>
+      </c>
+      <c r="E307" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
         <v>533</v>
       </c>
-      <c r="B303" t="s">
+      <c r="B308" t="s">
         <v>534</v>
       </c>
-      <c r="C303" t="s">
-        <v>93</v>
-      </c>
-      <c r="D303" t="s">
+      <c r="C308" t="s">
+        <v>93</v>
+      </c>
+      <c r="D308" t="s">
         <v>664</v>
       </c>
-      <c r="E303" t="s">
+      <c r="E308" t="s">
         <v>12</v>
       </c>
     </row>
